--- a/daha/files/daha-skill-practice.xlsx
+++ b/daha/files/daha-skill-practice.xlsx
@@ -1566,6 +1566,44 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 화면에 바로 복사할 수 있는 글로 보여 주고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일은 만들지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -2095,6 +2133,139 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 화면에 표로 보여 주고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 표를 엑셀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.xlsx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 이름은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상담일지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -2387,6 +2558,158 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.docx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 장으로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 이름은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사례회의자료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -2745,6 +3068,177 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 엑셀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.xlsx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요일별 표를 위에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핵심 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">줄 요약을 표 아래에 넣고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 이름은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주간업무보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -3225,6 +3719,44 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 문자에 바로 붙여넣을 수 있게 화면에 글로만 보여 주고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일은 만들지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -3707,6 +4239,139 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.docx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세부 일정과 예산 항목은 표로 넣고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 이름은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사업계획서초안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사업명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -3980,6 +4645,158 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 엑셀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.xlsx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첫 시트는 문항별 평균 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 수 표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">평균은 수식으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">둘째 시트는 서술 응답 분류로 하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고칠 점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가지는 화면에 글로 보여 줍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -4338,6 +5155,63 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.docx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 장의 편지 양식으로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -4799,6 +5673,101 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.docx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세로 한 장으로 만들어 내려받을 수 있게 하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문자용 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자 버전은 화면에 따로 보여 줍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -5195,6 +6164,196 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.docx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">할 일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">담당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 표로 넣고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 이름은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회의록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -5512,6 +6671,101 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.docx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 장으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본문 글자 크기 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16pt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이상으로 만들어 내려받을 수 있게 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -5834,6 +7088,44 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">같은 과장 표현은 쓰지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과는 보고서에 바로 붙여넣을 수 있게 화면에 글로 보여 주고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">달성률 계산은 표로 함께 보여 줍니다</t>
     </r>
     <r>
       <rPr>
@@ -6475,7 +7767,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">후속 조치</t>
+      <t xml:space="preserve">후속 조치 → 엑셀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.xlsx) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6B7280"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일로 내려받기</t>
     </r>
   </si>
   <si>
@@ -10823,11 +12134,11 @@
       </c>
       <c r="H5" s="18" t="str">
         <f aca="false">IF(B5="","","당신은 사회복지법인 다하의 "&amp;B5&amp;" 도우미입니다. "&amp;C5&amp;" 사용합니다. 입력되는 재료는 "&amp;D5&amp;"입니다. 결과는 "&amp;E5&amp;" 형식으로 정리합니다. "&amp;F5&amp;". 다음은 하지 않습니다: "&amp;G5&amp;". 실명 · 연락처 · 주소가 보이면 먼저 지우고 다시 입력해 달라고 안내합니다.")</f>
-        <v>당신은 사회복지법인 다하의 방문상담 기록 도우미입니다. 가정방문 후 메모를 방문기록지로 정리할 때 사용합니다. 입력되는 재료는 방문 메모(가명)입니다. 결과는 표: 방문일 | 대상자 | 주거 환경 | 건강·생활 상태 | 요청 사항 | 후속 조치 형식으로 정리합니다. 메모에 있는 사실만 · 문장은 "~함"으로. 다음은 하지 않습니다: 추측 · 진단 표현 · 실명. 실명 · 연락처 · 주소가 보이면 먼저 지우고 다시 입력해 달라고 안내합니다.</v>
+        <v>당신은 사회복지법인 다하의 방문상담 기록 도우미입니다. 가정방문 후 메모를 방문기록지로 정리할 때 사용합니다. 입력되는 재료는 방문 메모(가명)입니다. 결과는 표: 방문일 | 대상자 | 주거 환경 | 건강·생활 상태 | 요청 사항 | 후속 조치 → 엑셀(.xlsx) 파일로 내려받기 형식으로 정리합니다. 메모에 있는 사실만 · 문장은 "~함"으로. 다음은 하지 않습니다: 추측 · 진단 표현 · 실명. 실명 · 연락처 · 주소가 보이면 먼저 지우고 다시 입력해 달라고 안내합니다.</v>
       </c>
       <c r="I5" s="18" t="str">
         <f aca="false">IF(B5="","","다하 "&amp;B5&amp;" 스킬을 만들어 줘. 이름은 "&amp;A5&amp;". "&amp;C5&amp;" 쓸 거야. "&amp;D5&amp;"를 넣으면 "&amp;E5&amp;"로 정리해 줘. 규칙: "&amp;F5&amp;". 하지 말 것: "&amp;G5&amp;".")</f>
-        <v>다하 방문상담 기록 스킬을 만들어 줘. 이름은 daha-home-visit. 가정방문 후 메모를 방문기록지로 정리할 때 쓸 거야. 방문 메모(가명)를 넣으면 표: 방문일 | 대상자 | 주거 환경 | 건강·생활 상태 | 요청 사항 | 후속 조치로 정리해 줘. 규칙: 메모에 있는 사실만 · 문장은 "~함"으로. 하지 말 것: 추측 · 진단 표현 · 실명.</v>
+        <v>다하 방문상담 기록 스킬을 만들어 줘. 이름은 daha-home-visit. 가정방문 후 메모를 방문기록지로 정리할 때 쓸 거야. 방문 메모(가명)를 넣으면 표: 방문일 | 대상자 | 주거 환경 | 건강·생활 상태 | 요청 사항 | 후속 조치 → 엑셀(.xlsx) 파일로 내려받기로 정리해 줘. 규칙: 메모에 있는 사실만 · 문장은 "~함"으로. 하지 말 것: 추측 · 진단 표현 · 실명.</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
